--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -422,39 +422,49 @@
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prep_time</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>battle_time</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>settle_time</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>enemies_per_wave</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>spawn_interval</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>initial_delay</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>respawn_delay</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>spawn_radius</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>grant_seed</t>
         </is>
       </c>
     </row>
@@ -464,39 +474,49 @@
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>string!</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>int!#range=[1,100]</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>float!#range=[0.01,10]</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>float!#range=[0,60]</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>float!#range=[0,60]</t>
+          <t>float</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int!</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>float!</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>float!#range=[0.5,50]</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>SeedType</t>
         </is>
       </c>
     </row>
@@ -506,21 +526,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>c</t>
@@ -537,6 +542,31 @@
         </is>
       </c>
       <c r="H3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
@@ -548,65 +578,149 @@
           <t>##comment</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>编号</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>波次</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>显示名</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>每波敌人数</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>同波内两只之间的间隔</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>开局到第一波的等待</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>清完一波到下一波的等待</t>
+          <t>备战时长</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>战斗时长</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>结算时长</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>敌人数</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>刷怪间隔</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>出生环半径</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>战备配给种子</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="n">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>默认波次</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>首波侵袭</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>5</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Fire</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>疾跑蜂拥</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Elec</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>精英试炼</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.25</v>
       </c>
-      <c r="F5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="L7" t="n">
         <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Ice</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -1,34 +1,163 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFDA802-6D53-4586-B988-36BFD423C6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3945" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>prep_time</t>
+  </si>
+  <si>
+    <t>battle_time</t>
+  </si>
+  <si>
+    <t>settle_time</t>
+  </si>
+  <si>
+    <t>enemies_per_wave</t>
+  </si>
+  <si>
+    <t>spawn_interval</t>
+  </si>
+  <si>
+    <t>spawn_radius</t>
+  </si>
+  <si>
+    <t>grant_seed</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string!</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>int!</t>
+  </si>
+  <si>
+    <t>float!</t>
+  </si>
+  <si>
+    <t>float!#range=[0.5,50]</t>
+  </si>
+  <si>
+    <t>SeedType</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>波次</t>
+  </si>
+  <si>
+    <t>显示名</t>
+  </si>
+  <si>
+    <t>备战时长</t>
+  </si>
+  <si>
+    <t>战斗时长</t>
+  </si>
+  <si>
+    <t>结算时长</t>
+  </si>
+  <si>
+    <t>敌人数</t>
+  </si>
+  <si>
+    <t>刷怪间隔</t>
+  </si>
+  <si>
+    <t>出生环半径</t>
+  </si>
+  <si>
+    <t>战备配给种子</t>
+  </si>
+  <si>
+    <t>首波侵袭</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>疾跑蜂拥</t>
+  </si>
+  <si>
+    <t>Elec</t>
+  </si>
+  <si>
+    <t>精英试炼</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +176,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,322 +478,232 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="9" max="9" width="11.25" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>prep_time</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>battle_time</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>settle_time</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>enemies_per_wave</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>spawn_interval</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>spawn_radius</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>grant_seed</t>
-        </is>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string!</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>int!</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>float!</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>float!#range=[0.5,50]</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>SeedType</t>
-        </is>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>c</t>
-        </is>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>##comment</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>波次</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>显示名</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>备战时长</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>战斗时长</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>结算时长</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>敌人数</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>刷怪间隔</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>出生环半径</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>战备配给种子</t>
-        </is>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5">
-      <c r="E5" t="n">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>首波侵袭</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5">
         <v>10</v>
       </c>
-      <c r="H5" t="n">
+      <c r="E5">
         <v>30</v>
       </c>
-      <c r="I5" t="n">
+      <c r="F5">
         <v>8</v>
       </c>
-      <c r="J5" t="n">
+      <c r="G5">
         <v>6</v>
       </c>
-      <c r="K5" t="n">
+      <c r="H5">
         <v>0.4</v>
       </c>
-      <c r="L5" t="n">
+      <c r="I5">
         <v>5</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Fire</t>
-        </is>
+      <c r="J5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="6">
-      <c r="E6" t="n">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B6">
         <v>2</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>疾跑蜂拥</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
+      <c r="E6">
         <v>30</v>
       </c>
-      <c r="I6" t="n">
+      <c r="F6">
         <v>8</v>
       </c>
-      <c r="J6" t="n">
+      <c r="G6">
         <v>10</v>
       </c>
-      <c r="K6" t="n">
+      <c r="H6">
         <v>0.3</v>
       </c>
-      <c r="L6" t="n">
+      <c r="I6">
         <v>5</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Elec</t>
-        </is>
+      <c r="J6" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="7">
-      <c r="E7" t="n">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>精英试炼</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7">
         <v>10</v>
       </c>
-      <c r="H7" t="n">
+      <c r="E7">
         <v>30</v>
       </c>
-      <c r="I7" t="n">
+      <c r="F7">
         <v>8</v>
       </c>
-      <c r="J7" t="n">
+      <c r="G7">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
+      <c r="H7">
         <v>0.25</v>
       </c>
-      <c r="L7" t="n">
+      <c r="I7">
         <v>5</v>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Ice</t>
-        </is>
+      <c r="J7" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFDA802-6D53-4586-B988-36BFD423C6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39668D6F-DB5F-406F-BA90-4ED666EFCA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="3810" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4824" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -45,9 +45,6 @@
     <t>settle_time</t>
   </si>
   <si>
-    <t>enemies_per_wave</t>
-  </si>
-  <si>
     <t>spawn_interval</t>
   </si>
   <si>
@@ -69,9 +66,6 @@
     <t>float</t>
   </si>
   <si>
-    <t>int!</t>
-  </si>
-  <si>
     <t>float!</t>
   </si>
   <si>
@@ -103,9 +97,6 @@
   </si>
   <si>
     <t>结算时长</t>
-  </si>
-  <si>
-    <t>敌人数</t>
   </si>
   <si>
     <t>刷怪间隔</t>
@@ -479,14 +470,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="11.25" customWidth="1"/>
-    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.21875" customWidth="1"/>
+    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -514,112 +505,100 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>9</v>
       </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>16</v>
       </c>
-      <c r="J2" t="s">
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I4" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -631,24 +610,21 @@
         <v>8</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="H5">
-        <v>0.4</v>
-      </c>
-      <c r="I5">
         <v>5</v>
       </c>
-      <c r="J5" t="s">
-        <v>31</v>
+      <c r="I5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -660,24 +636,21 @@
         <v>8</v>
       </c>
       <c r="G6">
-        <v>10</v>
+        <v>0.3</v>
       </c>
       <c r="H6">
-        <v>0.3</v>
-      </c>
-      <c r="I6">
         <v>5</v>
       </c>
-      <c r="J6" t="s">
-        <v>33</v>
+      <c r="I6" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -689,16 +662,13 @@
         <v>8</v>
       </c>
       <c r="G7">
-        <v>12</v>
+        <v>0.25</v>
       </c>
       <c r="H7">
-        <v>0.25</v>
-      </c>
-      <c r="I7">
         <v>5</v>
       </c>
-      <c r="J7" t="s">
-        <v>35</v>
+      <c r="I7" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityHub\Unity Project\deepseaoil\ConfigWorkspace\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39668D6F-DB5F-406F-BA90-4ED666EFCA76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B32FB81-C6D1-4453-A0B7-B7460C474DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4824" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="255" yWindow="3060" windowWidth="12660" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -48,9 +48,6 @@
     <t>spawn_interval</t>
   </si>
   <si>
-    <t>spawn_radius</t>
-  </si>
-  <si>
     <t>grant_seed</t>
   </si>
   <si>
@@ -69,9 +66,6 @@
     <t>float!</t>
   </si>
   <si>
-    <t>float!#range=[0.5,50]</t>
-  </si>
-  <si>
     <t>SeedType</t>
   </si>
   <si>
@@ -100,9 +94,6 @@
   </si>
   <si>
     <t>刷怪间隔</t>
-  </si>
-  <si>
-    <t>出生环半径</t>
   </si>
   <si>
     <t>战备配给种子</t>
@@ -470,14 +461,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="8" max="8" width="11.21875" customWidth="1"/>
-    <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -502,103 +492,91 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
         <v>8</v>
       </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="I2" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" t="s">
-        <v>17</v>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5">
         <v>10</v>
@@ -612,19 +590,16 @@
       <c r="G5">
         <v>0.4</v>
       </c>
-      <c r="H5">
-        <v>5</v>
-      </c>
-      <c r="I5" t="s">
-        <v>28</v>
+      <c r="H5" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D6">
         <v>10</v>
@@ -638,19 +613,16 @@
       <c r="G6">
         <v>0.3</v>
       </c>
-      <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6" t="s">
-        <v>30</v>
+      <c r="H6" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>10</v>
@@ -664,11 +636,8 @@
       <c r="G7">
         <v>0.25</v>
       </c>
-      <c r="H7">
-        <v>5</v>
-      </c>
-      <c r="I7" t="s">
-        <v>32</v>
+      <c r="H7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B32FB81-C6D1-4453-A0B7-B7460C474DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="3060" windowWidth="12660" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="14940" windowHeight="9900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -109,43 +111,373 @@
   </si>
   <si>
     <t>Elec</t>
-  </si>
-  <si>
-    <t>精英试炼</t>
-  </si>
-  <si>
-    <t>Ice</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -153,24 +485,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -455,19 +1073,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +1111,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -519,7 +1137,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -545,7 +1163,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -571,7 +1189,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5">
         <v>1</v>
       </c>
@@ -594,7 +1212,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8">
       <c r="B6">
         <v>2</v>
       </c>
@@ -617,32 +1235,9 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>0.25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B32FB81-C6D1-4453-A0B7-B7460C474DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="255" yWindow="3060" windowWidth="12660" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -120,32 +122,368 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -153,24 +491,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -455,19 +1079,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="7"/>
   <cols>
-    <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +1117,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -519,7 +1143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -545,7 +1169,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -571,7 +1195,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5">
         <v>1</v>
       </c>
@@ -579,10 +1203,10 @@
         <v>24</v>
       </c>
       <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>10</v>
-      </c>
-      <c r="E5">
-        <v>30</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -594,7 +1218,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8">
       <c r="B6">
         <v>2</v>
       </c>
@@ -617,7 +1241,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7">
         <v>3</v>
       </c>
@@ -641,8 +1265,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -101,16 +101,22 @@
     <t>战备配给种子</t>
   </si>
   <si>
-    <t>首波侵袭</t>
+    <t>教学</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>第一关</t>
+  </si>
+  <si>
+    <t>第二关</t>
+  </si>
+  <si>
+    <t>第三关</t>
   </si>
   <si>
     <t>Fire</t>
-  </si>
-  <si>
-    <t>疾跑蜂拥</t>
-  </si>
-  <si>
-    <t>Elec</t>
   </si>
 </sst>
 </file>
@@ -123,14 +129,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -586,148 +585,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1079,8 +1078,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
@@ -1197,7 +1196,7 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E5">
         <v>30</v>
@@ -1220,10 +1219,10 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -1232,7 +1231,53 @@
         <v>0.3</v>
       </c>
       <c r="H6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>0.2</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>8</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>8</v>
+      </c>
+      <c r="G8">
+        <v>0.3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14940" windowHeight="9900"/>
+    <workbookView windowWidth="15160" windowHeight="10460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -113,10 +113,16 @@
     <t>第二关</t>
   </si>
   <si>
-    <t>第三关</t>
+    <t>第三关(掉落）</t>
   </si>
   <si>
     <t>Fire</t>
+  </si>
+  <si>
+    <t>第三四关</t>
+  </si>
+  <si>
+    <t>第四关</t>
   </si>
 </sst>
 </file>
@@ -1078,8 +1084,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
@@ -1196,7 +1202,7 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>30</v>
@@ -1219,10 +1225,10 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -1242,10 +1248,10 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F7">
         <v>8</v>
@@ -1265,18 +1271,64 @@
         <v>28</v>
       </c>
       <c r="D8">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G8">
         <v>0.3</v>
       </c>
       <c r="H8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>0.2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>0.2</v>
+      </c>
+      <c r="H10" t="s">
         <v>29</v>
       </c>
     </row>

--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14940" windowHeight="9900"/>
+    <workbookView windowWidth="15160" windowHeight="10460"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -101,16 +101,28 @@
     <t>战备配给种子</t>
   </si>
   <si>
-    <t>首波侵袭</t>
+    <t>教学</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>第一关</t>
+  </si>
+  <si>
+    <t>第二关</t>
+  </si>
+  <si>
+    <t>第三关(掉落）</t>
   </si>
   <si>
     <t>Fire</t>
   </si>
   <si>
-    <t>疾跑蜂拥</t>
-  </si>
-  <si>
-    <t>Elec</t>
+    <t>第三四关</t>
+  </si>
+  <si>
+    <t>第四关</t>
   </si>
 </sst>
 </file>
@@ -123,14 +135,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -586,148 +591,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1079,8 +1084,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
@@ -1197,7 +1202,7 @@
         <v>24</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E5">
         <v>30</v>
@@ -1220,10 +1225,10 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="F6">
         <v>8</v>
@@ -1232,7 +1237,99 @@
         <v>0.3</v>
       </c>
       <c r="H6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
+      </c>
+      <c r="D7">
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <v>60</v>
+      </c>
+      <c r="F7">
+        <v>8</v>
+      </c>
+      <c r="G7">
+        <v>0.2</v>
+      </c>
+      <c r="H7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>0.3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+      <c r="G9">
+        <v>0.2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>0.2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -123,6 +123,15 @@
   </si>
   <si>
     <t>第四关</t>
+  </si>
+  <si>
+    <t>第五关1</t>
+  </si>
+  <si>
+    <t>第五关2</t>
+  </si>
+  <si>
+    <t>第五关3</t>
   </si>
 </sst>
 </file>
@@ -1084,7 +1093,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
     <col min="8" max="8" width="13" customWidth="1"/>
@@ -1297,7 +1306,7 @@
         <v>3</v>
       </c>
       <c r="E9">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1320,7 +1329,7 @@
         <v>4</v>
       </c>
       <c r="E10">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1329,6 +1338,75 @@
         <v>0.2</v>
       </c>
       <c r="H10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8">
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>0.3</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
+      <c r="B12">
+        <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12">
+        <v>7</v>
+      </c>
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12">
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <v>0.3</v>
+      </c>
+      <c r="H12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
+      <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>50</v>
+      </c>
+      <c r="F13">
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <v>0.3</v>
+      </c>
+      <c r="H13" t="s">
         <v>29</v>
       </c>
     </row>

--- a/ConfigWorkspace/Data/wave.xlsx
+++ b/ConfigWorkspace/Data/wave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="T:\GAMES\deepseaoil\ConfigWorkspace\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CD00D78-6282-4C79-9112-2387C5354B8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA045063-51F3-4632-8155-C90F3EA6E7F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4450" yWindow="1970" windowWidth="15080" windowHeight="11670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3270" yWindow="2730" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
   <si>
     <t>##var</t>
   </si>
@@ -211,6 +211,18 @@
   </si>
   <si>
     <t>describe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>教程关</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -566,18 +578,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.75" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" style="1" customWidth="1"/>
     <col min="9" max="9" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +618,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -635,7 +647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
@@ -664,7 +676,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -693,7 +705,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1">
         <v>1</v>
       </c>
@@ -719,7 +731,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <v>2</v>
       </c>
@@ -745,7 +757,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <v>3</v>
       </c>
@@ -771,7 +783,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <v>4</v>
       </c>
@@ -797,7 +809,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <v>5</v>
       </c>
@@ -823,7 +835,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <v>6</v>
       </c>
@@ -849,7 +861,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <v>7</v>
       </c>
@@ -875,7 +887,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <v>8</v>
       </c>
@@ -901,7 +913,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>9</v>
       </c>
@@ -927,7 +939,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="1">
         <v>10</v>
       </c>
@@ -953,7 +965,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>11</v>
       </c>
@@ -979,7 +991,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
         <v>12</v>
       </c>
@@ -1005,7 +1017,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>13</v>
       </c>
@@ -1031,7 +1043,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>14</v>
       </c>
@@ -1057,7 +1069,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>15</v>
       </c>
@@ -1081,6 +1093,32 @@
       </c>
       <c r="I19" s="3" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.15">
+      <c r="B20" s="1">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="1">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1">
+        <v>30</v>
+      </c>
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="G20" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
